--- a/results/tables/Tabla_3_centroides_originales_estandarizados.xlsx
+++ b/results/tables/Tabla_3_centroides_originales_estandarizados.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -384,184 +384,143 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Petróleo crudo</t>
+          <t>Asfaltos</t>
         </is>
       </c>
       <c r="B2">
-        <v>6272.5</v>
-      </c>
-      <c r="C2">
-        <v>1.14</v>
+        <v>54.3</v>
       </c>
       <c r="D2">
-        <v>3544.6</v>
-      </c>
-      <c r="E2">
-        <v>-0.61</v>
+        <v>105.8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Otros primarias</t>
+          <t>Avtur</t>
         </is>
       </c>
       <c r="B3">
-        <v>27</v>
-      </c>
-      <c r="C3">
-        <v>-1.13</v>
+        <v>567.7</v>
       </c>
       <c r="D3">
-        <v>34.7</v>
-      </c>
-      <c r="E3">
-        <v>0.6</v>
+        <v>870.8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Gas natural</t>
+          <t>Carbón mineral</t>
         </is>
       </c>
       <c r="B4">
-        <v>433.6</v>
-      </c>
-      <c r="C4">
-        <v>-1.09</v>
+        <v>1871.3</v>
       </c>
       <c r="D4">
-        <v>2333.6</v>
-      </c>
-      <c r="E4">
-        <v>0.58</v>
+        <v>3857.6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Gas licuado de petróleo</t>
+          <t>Coque</t>
         </is>
       </c>
       <c r="B5">
-        <v>1646.2</v>
-      </c>
-      <c r="C5">
-        <v>-0.96</v>
+        <v>777.2</v>
       </c>
       <c r="D5">
-        <v>2395.6</v>
-      </c>
-      <c r="E5">
-        <v>0.51</v>
+        <v>1415.2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Coque</t>
+          <t>Gas licuado de petróleo</t>
         </is>
       </c>
       <c r="B6">
-        <v>706.1</v>
-      </c>
-      <c r="C6">
-        <v>-0.92</v>
+        <v>1779.6</v>
       </c>
       <c r="D6">
-        <v>1340.4</v>
-      </c>
-      <c r="E6">
-        <v>0.49</v>
+        <v>2408.3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Asfaltos</t>
+          <t>Gas natural</t>
         </is>
       </c>
       <c r="B7">
-        <v>44.7</v>
-      </c>
-      <c r="C7">
-        <v>-0.8100000000000001</v>
+        <v>636.4</v>
       </c>
       <c r="D7">
-        <v>104.1</v>
-      </c>
-      <c r="E7">
-        <v>0.43</v>
+        <v>2532</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Avtur</t>
+          <t>Gasolina</t>
         </is>
       </c>
       <c r="B8">
-        <v>543.5</v>
-      </c>
-      <c r="C8">
-        <v>-0.76</v>
+        <v>1659.5</v>
       </c>
       <c r="D8">
-        <v>843.3</v>
-      </c>
-      <c r="E8">
-        <v>0.41</v>
+        <v>2350.3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Carbón mineral</t>
+          <t>Otros no energético</t>
         </is>
       </c>
       <c r="B9">
-        <v>1720.4</v>
-      </c>
-      <c r="C9">
-        <v>-0.72</v>
+        <v>46</v>
       </c>
       <c r="D9">
-        <v>3673.2</v>
-      </c>
-      <c r="E9">
-        <v>0.38</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Otros no energético</t>
+          <t>Otros primarias</t>
         </is>
       </c>
       <c r="B10">
-        <v>42.3</v>
-      </c>
-      <c r="C10">
-        <v>-0.66</v>
+        <v>28</v>
       </c>
       <c r="D10">
-        <v>61</v>
-      </c>
-      <c r="E10">
-        <v>0.35</v>
+        <v>36.1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>Petróleo crudo</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>5934.4</v>
+      </c>
+      <c r="D11">
+        <v>3385</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>Cluster</t>
         </is>
       </c>
-      <c r="B11">
+      <c r="B12">
         <v>1</v>
       </c>
-      <c r="D11">
+      <c r="D12">
         <v>2</v>
       </c>
     </row>
